--- a/docs/03_test/社員一覧画面テスト.xlsx
+++ b/docs/03_test/社員一覧画面テスト.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\fullness\cs-training\Web_App_Exercise\docs\03_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCF16B6F-774C-4DC9-8F29-D6A0D024803C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{919B70F7-719B-49E9-A9E5-1BD3DEE82F0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{EDAA8412-2266-41CD-B1C8-4C46E6C24210}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{EDAA8412-2266-41CD-B1C8-4C46E6C24210}"/>
   </bookViews>
   <sheets>
-    <sheet name="部署登録テスト" sheetId="1" r:id="rId1"/>
+    <sheet name="社員一覧テスト" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -404,6 +404,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -411,9 +414,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -943,10 +943,10 @@
       <c r="D5" s="10"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="11" t="s">
@@ -957,16 +957,16 @@
       <c r="D7" s="3"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B18" s="15"/>
+      <c r="B18" s="16"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B19" s="16" t="s">
+      <c r="B19" s="17" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="12" t="s">
@@ -978,7 +978,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="13"/>
-      <c r="B20" s="16"/>
+      <c r="B20" s="17"/>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
     </row>
@@ -1074,17 +1074,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="A6:D6"/>
     <mergeCell ref="A47:C47"/>
     <mergeCell ref="D19:D20"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="B19:B20"/>
     <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
